--- a/data/input/消费记录.xlsx
+++ b/data/input/消费记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,33 +531,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -572,19 +572,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1728</v>
+        <v>378</v>
       </c>
       <c r="Q2" t="n">
-        <v>1152</v>
+        <v>252</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
@@ -611,60 +611,60 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1728</v>
+        <v>378</v>
       </c>
       <c r="Q3" t="n">
-        <v>1152</v>
+        <v>252</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
@@ -691,60 +691,60 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1728</v>
+        <v>378</v>
       </c>
       <c r="Q4" t="n">
-        <v>1152</v>
+        <v>252</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORD000002</t>
+          <t>ORD000001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -771,33 +771,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CU001</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>张小美</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>7480</v>
+        <v>2520</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -812,19 +812,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1122</v>
+        <v>378</v>
       </c>
       <c r="Q5" t="n">
-        <v>748</v>
+        <v>252</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
@@ -851,60 +851,60 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CU001</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>张小美</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>7480</v>
+        <v>4350</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>王医生</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1122</v>
+        <v>652.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>748</v>
+        <v>435</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORD000005</t>
+          <t>ORD000002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,33 +931,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>玻尿酸填充</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>3040</v>
+        <v>4350</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -972,19 +972,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>456</v>
+        <v>652.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>304</v>
+        <v>435</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORD000006</t>
+          <t>ORD000002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1011,60 +1011,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>11520</v>
+        <v>4350</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>王医生</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1728</v>
+        <v>652.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1152</v>
+        <v>435</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORD000006</t>
+          <t>ORD000002</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1091,60 +1091,60 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>11520</v>
+        <v>4350</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>王医生</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1728</v>
+        <v>652.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1152</v>
+        <v>435</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORD000006</t>
+          <t>ORD000003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1171,33 +1171,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1212,19 +1212,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1728</v>
+        <v>378</v>
       </c>
       <c r="Q10" t="n">
-        <v>1152</v>
+        <v>252</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORD000006</t>
+          <t>ORD000003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1251,60 +1251,60 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>王医生</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1728</v>
+        <v>378</v>
       </c>
       <c r="Q11" t="n">
-        <v>1152</v>
+        <v>252</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORD000007</t>
+          <t>ORD000003</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1331,33 +1331,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>玻尿酸填充</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>3040</v>
+        <v>2520</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1372,19 +1372,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>456</v>
+        <v>378</v>
       </c>
       <c r="Q12" t="n">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORD000007</t>
+          <t>ORD000004</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORD000007</t>
+          <t>ORD000004</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORD000008</t>
+          <t>ORD000005</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1571,33 +1571,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>4350</v>
+        <v>11520</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>652.5</v>
+        <v>1728</v>
       </c>
       <c r="Q15" t="n">
-        <v>435</v>
+        <v>1152</v>
       </c>
       <c r="R15" t="inlineStr"/>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORD000008</t>
+          <t>ORD000006</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1651,60 +1651,60 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>4350</v>
+        <v>3040</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>652.5</v>
+        <v>456</v>
       </c>
       <c r="Q16" t="n">
-        <v>435</v>
+        <v>304</v>
       </c>
       <c r="R16" t="inlineStr"/>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORD000008</t>
+          <t>ORD000006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1731,60 +1731,60 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>4350</v>
+        <v>3040</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>652.5</v>
+        <v>456</v>
       </c>
       <c r="Q17" t="n">
-        <v>435</v>
+        <v>304</v>
       </c>
       <c r="R17" t="inlineStr"/>
     </row>
@@ -1796,48 +1796,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORD000011</t>
+          <t>ORD000007</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>上海浦东店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>7480</v>
+        <v>6708</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1852,21 +1852,25 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1122</v>
+        <v>1006.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>748</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
+        <v>670.8</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>套餐项目消费</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1876,58 +1880,58 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORD000011</t>
+          <t>ORD000008</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>上海浦东店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>7480</v>
+        <v>5248</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1941,12 +1945,16 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1122</v>
+        <v>787.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>748</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <v>524.8</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>套餐项目消费</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1956,7 +1964,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORD000012</t>
+          <t>ORD000010</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1971,33 +1979,33 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU007</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>吴莹莹</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I006</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>瘦脸针</t>
+          <t>水光针</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>2520</v>
+        <v>833</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2021,10 +2029,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>378</v>
+        <v>124.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>252</v>
+        <v>83.3</v>
       </c>
       <c r="R20" t="inlineStr"/>
     </row>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ORD000013</t>
+          <t>ORD000011</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2061,23 +2069,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>双眼皮手术</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>833</v>
+        <v>7480</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2101,10 +2109,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>124.95</v>
+        <v>1122</v>
       </c>
       <c r="Q21" t="n">
-        <v>83.3</v>
+        <v>748</v>
       </c>
       <c r="R21" t="inlineStr"/>
     </row>
@@ -2116,7 +2124,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ORD000016</t>
+          <t>ORD000011</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2131,43 +2139,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CU005</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>孙倩倩</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>双眼皮手术</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>4350</v>
+        <v>7480</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2181,10 +2189,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>652.5</v>
+        <v>1122</v>
       </c>
       <c r="Q22" t="n">
-        <v>435</v>
+        <v>748</v>
       </c>
       <c r="R22" t="inlineStr"/>
     </row>
@@ -2196,75 +2204,75 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORD000017</t>
+          <t>ORD000013</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>上海浦东店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CU007</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>吴莹莹</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>玻尿酸填充</t>
+          <t>双眼皮手术</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>3040</v>
+        <v>7480</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>李医生</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>456</v>
+        <v>1122</v>
       </c>
       <c r="Q23" t="n">
-        <v>304</v>
+        <v>748</v>
       </c>
       <c r="R23" t="inlineStr"/>
     </row>
@@ -2276,27 +2284,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ORD000018</t>
+          <t>ORD000013</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>上海浦东店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2317,7 +2325,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2332,12 +2340,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2356,48 +2364,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ORD000018</t>
+          <t>ORD000014</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>上海浦东店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU008</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>郑思思</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>7480</v>
+        <v>2520</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2412,19 +2420,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1122</v>
+        <v>378</v>
       </c>
       <c r="Q25" t="n">
-        <v>748</v>
+        <v>252</v>
       </c>
       <c r="R25" t="inlineStr"/>
     </row>
@@ -2436,7 +2444,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ORD000018</t>
+          <t>ORD000016</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2451,43 +2459,43 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>7480</v>
+        <v>11520</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>李医生</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2501,10 +2509,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1122</v>
+        <v>1728</v>
       </c>
       <c r="Q26" t="n">
-        <v>748</v>
+        <v>1152</v>
       </c>
       <c r="R26" t="inlineStr"/>
     </row>
@@ -2516,7 +2524,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ORD000019</t>
+          <t>ORD000017</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2531,43 +2539,43 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>水光针</t>
         </is>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>4350</v>
+        <v>833</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2581,10 +2589,10 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>652.5</v>
+        <v>124.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>435</v>
+        <v>83.3</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
@@ -2596,7 +2604,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ORD000019</t>
+          <t>ORD000020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2611,60 +2619,60 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>4350</v>
+        <v>11520</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>652.5</v>
+        <v>1728</v>
       </c>
       <c r="Q28" t="n">
-        <v>435</v>
+        <v>1152</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
@@ -2676,7 +2684,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ORD000019</t>
+          <t>ORD000020</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2691,60 +2699,60 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>4350</v>
+        <v>11520</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>李医生</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>652.5</v>
+        <v>1728</v>
       </c>
       <c r="Q29" t="n">
-        <v>435</v>
+        <v>1152</v>
       </c>
       <c r="R29" t="inlineStr"/>
     </row>
@@ -2756,7 +2764,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ORD000019</t>
+          <t>ORD000020</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2771,60 +2779,60 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>4350</v>
+        <v>11520</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>652.5</v>
+        <v>1728</v>
       </c>
       <c r="Q30" t="n">
-        <v>435</v>
+        <v>1152</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
@@ -2836,7 +2844,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ORD000022</t>
+          <t>ORD000021</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2851,62 +2859,66 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU008</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>郑思思</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>王医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1728</v>
+        <v>378</v>
       </c>
       <c r="Q31" t="n">
-        <v>1152</v>
-      </c>
-      <c r="R31" t="inlineStr"/>
+        <v>252</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>上月数据</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2916,77 +2928,81 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ORD000023</t>
+          <t>ORD000022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU007</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>吴莹莹</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>833</v>
+        <v>4350</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>王医生</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>124.95</v>
+        <v>652.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
+        <v>435</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>上月数据</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3001,53 +3017,53 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>双眼皮手术</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>833</v>
+        <v>7480</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>D002</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>李医生</t>
+          <t>张医生</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3061,252 +3077,16 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>124.95</v>
+        <v>1122</v>
       </c>
       <c r="Q33" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REC000033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ORD000024</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>广州天河店</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CU004</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>赵丽丽</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>I005</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>双眼皮手术</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>7480</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>王医生</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>周咨询师</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>1122</v>
-      </c>
-      <c r="Q34" t="n">
         <v>748</v>
       </c>
-      <c r="R34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REC000034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ORD000024</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>广州天河店</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>CU004</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>赵丽丽</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>I005</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>双眼皮手术</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>7480</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>王医生</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>周咨询师</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>1122</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>748</v>
-      </c>
-      <c r="R35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>REC000035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ORD000024</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>广州天河店</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CU004</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>赵丽丽</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>I005</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>双眼皮手术</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>7480</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>王医生</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>周咨询师</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>1122</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>748</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>上月数据</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
